--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B073E79-CB14-4363-9521-F2C0245D81DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF183EBF-9326-4033-B5E6-3E3D79CAA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="123">
   <si>
     <t>Produtos</t>
   </si>
@@ -385,6 +385,18 @@
   </si>
   <si>
     <t>São Sebastião</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Centro Clínico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blusa feminina manga longa tamanho M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blusa feminina manga longa tamanho P </t>
   </si>
 </sst>
 </file>
@@ -2610,10 +2622,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36963CDE-E660-488E-A4B2-DCAAECEBA598}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" customWidth="1"/>
+    <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="95.42578125" customWidth="1"/>
@@ -3113,6 +3125,146 @@
         <v>46300</v>
       </c>
     </row>
+    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="26">
+        <v>10</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="26">
+        <v>2</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="26">
+        <v>6</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="26">
+        <v>2</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="26">
+        <v>6</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="26">
+        <v>2</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="15">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="26">
+        <v>6</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="15">
+        <v>46301</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF183EBF-9326-4033-B5E6-3E3D79CAA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F888D856-6DFE-428E-9BED-D4CEF3E1BBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="122">
   <si>
     <t>Produtos</t>
   </si>
@@ -385,9 +385,6 @@
   </si>
   <si>
     <t>São Sebastião</t>
-  </si>
-  <si>
-    <t>Não</t>
   </si>
   <si>
     <t>Centro Clínico</t>
@@ -3138,8 +3135,8 @@
       <c r="D26" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>119</v>
+      <c r="E26" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="15">
         <v>46301</v>
@@ -3156,10 +3153,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F27" s="15">
         <v>46301</v>
@@ -3176,10 +3173,10 @@
         <v>7</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="15">
         <v>46301</v>
@@ -3187,7 +3184,7 @@
     </row>
     <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B29" s="26">
         <v>2</v>
@@ -3196,10 +3193,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="15">
         <v>46301</v>
@@ -3207,7 +3204,7 @@
     </row>
     <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="26">
         <v>6</v>
@@ -3216,10 +3213,10 @@
         <v>7</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="15">
         <v>46301</v>
@@ -3236,10 +3233,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F31" s="15">
         <v>46301</v>
@@ -3256,10 +3253,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" s="17" t="s">
         <v>119</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F32" s="15">
         <v>46301</v>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F888D856-6DFE-428E-9BED-D4CEF3E1BBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E9D121-0192-427A-9E59-9D7A1FB928A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="123">
   <si>
     <t>Produtos</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t xml:space="preserve">Blusa feminina manga longa tamanho P </t>
+  </si>
+  <si>
+    <t>Não</t>
   </si>
 </sst>
 </file>
@@ -624,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -711,6 +714,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2619,7 +2628,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36963CDE-E660-488E-A4B2-DCAAECEBA598}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
@@ -3243,23 +3252,43 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="29">
         <v>6</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="30" t="s">
         <v>119</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="31">
         <v>46301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="35">
+        <v>20</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="20">
+        <v>46303</v>
       </c>
     </row>
   </sheetData>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E9D121-0192-427A-9E59-9D7A1FB928A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE061016-1EB2-4E20-8FB7-66DC1717E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="125">
   <si>
     <t>Produtos</t>
   </si>
@@ -396,7 +396,13 @@
     <t xml:space="preserve">Blusa feminina manga longa tamanho P </t>
   </si>
   <si>
-    <t>Não</t>
+    <t>QNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detergente </t>
+  </si>
+  <si>
+    <t>Vicente Pires</t>
   </si>
 </sst>
 </file>
@@ -2628,7 +2634,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36963CDE-E660-488E-A4B2-DCAAECEBA598}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
@@ -3284,10 +3290,50 @@
       <c r="D33" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="20">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="35">
+        <v>1</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="20">
+      <c r="E34" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="20">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="35">
+        <v>5</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="20">
         <v>46303</v>
       </c>
     </row>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE061016-1EB2-4E20-8FB7-66DC1717E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7DCCBC-E12D-4DB6-87EB-BFE7F0793F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -336,9 +336,6 @@
     <t xml:space="preserve">Blusa feminina tamanho M </t>
   </si>
   <si>
-    <t>Blusa femina tamabho G</t>
-  </si>
-  <si>
     <t>Blusa masculina tamanho M</t>
   </si>
   <si>
@@ -403,6 +400,9 @@
   </si>
   <si>
     <t>Vicente Pires</t>
+  </si>
+  <si>
+    <t>Blusa femina tamanho G</t>
   </si>
 </sst>
 </file>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B10" s="26">
         <v>2</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="26">
         <v>1</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B12" s="26">
         <v>2</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="26">
         <v>4</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" s="26">
         <v>1</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B15" s="26">
         <v>1</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="26">
         <v>1</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17" s="26">
         <v>1</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B19" s="29">
         <v>1</v>
@@ -3010,7 +3010,7 @@
       <c r="D19" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="31">
@@ -3019,7 +3019,7 @@
     </row>
     <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" s="26">
         <v>2</v>
@@ -3030,7 +3030,7 @@
       <c r="D20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="15">
@@ -3039,7 +3039,7 @@
     </row>
     <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="26">
         <v>1</v>
@@ -3050,7 +3050,7 @@
       <c r="D21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="15">
@@ -3059,7 +3059,7 @@
     </row>
     <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" s="26">
         <v>1</v>
@@ -3070,7 +3070,7 @@
       <c r="D22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="15">
@@ -3079,7 +3079,7 @@
     </row>
     <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B23" s="26">
         <v>1</v>
@@ -3090,7 +3090,7 @@
       <c r="D23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="15">
@@ -3099,7 +3099,7 @@
     </row>
     <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="26">
         <v>2</v>
@@ -3110,7 +3110,7 @@
       <c r="D24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="15">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B25" s="32">
         <v>40</v>
@@ -3128,9 +3128,9 @@
         <v>7</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="33">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="26">
         <v>10</v>
@@ -3150,7 +3150,7 @@
       <c r="D26" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="15">
@@ -3168,9 +3168,9 @@
         <v>7</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="15">
@@ -3188,9 +3188,9 @@
         <v>7</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="15">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="26">
         <v>2</v>
@@ -3208,9 +3208,9 @@
         <v>7</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="15">
@@ -3219,7 +3219,7 @@
     </row>
     <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="26">
         <v>6</v>
@@ -3228,9 +3228,9 @@
         <v>7</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="15">
@@ -3239,7 +3239,7 @@
     </row>
     <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="26">
         <v>2</v>
@@ -3248,9 +3248,9 @@
         <v>7</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F31" s="15">
@@ -3259,7 +3259,7 @@
     </row>
     <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" s="29">
         <v>6</v>
@@ -3268,9 +3268,9 @@
         <v>7</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="31">
@@ -3279,7 +3279,7 @@
     </row>
     <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" s="35">
         <v>20</v>
@@ -3290,7 +3290,7 @@
       <c r="D33" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F33" s="20">
@@ -3308,9 +3308,9 @@
         <v>7</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="20">
@@ -3319,7 +3319,7 @@
     </row>
     <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="35">
         <v>5</v>
@@ -3328,9 +3328,9 @@
         <v>7</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E35" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="20">

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7DCCBC-E12D-4DB6-87EB-BFE7F0793F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ACABF9-B0D6-402E-97A3-1384A8DA1F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="127">
   <si>
     <t>Produtos</t>
   </si>
@@ -403,6 +403,12 @@
   </si>
   <si>
     <t>Blusa femina tamanho G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodo </t>
+  </si>
+  <si>
+    <t>Não</t>
   </si>
 </sst>
 </file>
@@ -2634,7 +2640,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36963CDE-E660-488E-A4B2-DCAAECEBA598}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
@@ -3337,6 +3343,26 @@
         <v>46303</v>
       </c>
     </row>
+    <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="32">
+        <v>1</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="33">
+        <v>46304</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ACABF9-B0D6-402E-97A3-1384A8DA1F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08AED26-6DB9-4A6F-84E6-A5340355B6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>

--- a/Suprimentos.xlsx
+++ b/Suprimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRISHJ00\Documents\Up\Suprimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08AED26-6DB9-4A6F-84E6-A5340355B6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AC8550-91A8-411C-843F-58BD7347019D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{101DF58F-0805-494F-86FF-0DF45E2C3859}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="132">
   <si>
     <t>Produtos</t>
   </si>
@@ -378,37 +378,52 @@
     <t>Marca texto CX</t>
   </si>
   <si>
+    <t>São Sebastião</t>
+  </si>
+  <si>
+    <t>Centro Clínico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blusa feminina manga longa tamanho M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blusa feminina manga longa tamanho P </t>
+  </si>
+  <si>
+    <t>QNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detergente </t>
+  </si>
+  <si>
+    <t>Vicente Pires</t>
+  </si>
+  <si>
+    <t>Blusa femina tamanho G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodo </t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Cinta EPI tamanho P</t>
+  </si>
+  <si>
+    <t>Álcool 1L</t>
+  </si>
+  <si>
+    <t>Recanto das Emas</t>
+  </si>
+  <si>
+    <t>Carrefour</t>
+  </si>
+  <si>
     <t>Amarradinho PCT</t>
   </si>
   <si>
-    <t>São Sebastião</t>
-  </si>
-  <si>
-    <t>Centro Clínico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blusa feminina manga longa tamanho M </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blusa feminina manga longa tamanho P </t>
-  </si>
-  <si>
-    <t>QNE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detergente </t>
-  </si>
-  <si>
-    <t>Vicente Pires</t>
-  </si>
-  <si>
-    <t>Blusa femina tamanho G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodo </t>
-  </si>
-  <si>
-    <t>Não</t>
+    <t>Resma 15 PCT</t>
   </si>
 </sst>
 </file>
@@ -2640,7 +2655,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36963CDE-E660-488E-A4B2-DCAAECEBA598}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
@@ -2825,7 +2840,7 @@
     </row>
     <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B10" s="26">
         <v>2</v>
@@ -2984,7 +2999,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="17" t="s">
         <v>109</v>
       </c>
       <c r="B18" s="26">
@@ -3004,7 +3019,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="17" t="s">
         <v>110</v>
       </c>
       <c r="B19" s="29">
@@ -3125,7 +3140,7 @@
     </row>
     <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B25" s="32">
         <v>40</v>
@@ -3134,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>13</v>
@@ -3145,7 +3160,7 @@
     </row>
     <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B26" s="26">
         <v>10</v>
@@ -3174,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>13</v>
@@ -3194,7 +3209,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>13</v>
@@ -3205,7 +3220,7 @@
     </row>
     <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B29" s="26">
         <v>2</v>
@@ -3214,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>13</v>
@@ -3225,7 +3240,7 @@
     </row>
     <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" s="26">
         <v>6</v>
@@ -3234,7 +3249,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>13</v>
@@ -3254,7 +3269,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>13</v>
@@ -3274,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>13</v>
@@ -3285,7 +3300,7 @@
     </row>
     <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B33" s="35">
         <v>20</v>
@@ -3314,7 +3329,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>13</v>
@@ -3325,7 +3340,7 @@
     </row>
     <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="35">
         <v>5</v>
@@ -3334,7 +3349,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>13</v>
@@ -3344,23 +3359,157 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="26">
+        <v>1</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="15">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="26">
+        <v>1</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="15">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="26">
+        <v>1</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B36" s="32">
-        <v>1</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="33">
-        <v>46304</v>
+      <c r="F38" s="15">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="26">
+        <v>1</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="15">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="26">
+        <v>2</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="15">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="26">
+        <v>1</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="15">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="26">
+        <v>1</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="15">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="26">
+        <v>1</v>
+      </c>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="15">
+        <v>46309</v>
       </c>
     </row>
   </sheetData>
